--- a/artfynd/A 7903-2024 artfynd.xlsx
+++ b/artfynd/A 7903-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1019,6 +1019,125 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>115073977</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57386</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Sopekärr/Intakan, Hålanda, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>338266</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6433790</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Födosökande i tät gran/björk/tall skog.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 7903-2024 artfynd.xlsx
+++ b/artfynd/A 7903-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1138,6 +1138,116 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>115074021</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57597</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Sopekärr/Intakan, Hålanda, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>338271</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6433813</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 7903-2024 artfynd.xlsx
+++ b/artfynd/A 7903-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1824,6 +1824,117 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>120338516</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57336</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Risveden/Sopekärr, Vg</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>338364</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6433774</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Spår av födosökande spillkråka</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 7903-2024 artfynd.xlsx
+++ b/artfynd/A 7903-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1594,10 +1594,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>116182876</v>
+        <v>116184071</v>
       </c>
       <c r="B10" t="n">
-        <v>8403</v>
+        <v>57281</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1606,34 +1606,33 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1643,13 +1642,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>338518</v>
+        <v>338000</v>
       </c>
       <c r="R10" t="n">
-        <v>6433849</v>
+        <v>6433828</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1683,7 +1682,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Noterade lodräta rader med hål efter björksplintborren på en 5 m hög björkhögstubbe.</t>
+          <t>Fann spillkråkehack efter födosök vid basen av ett medelgrovt torrträd. Stod ca 10 m söder om småvattnet i skogen.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1692,7 +1691,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1711,10 +1709,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>116184071</v>
+        <v>120338516</v>
       </c>
       <c r="B11" t="n">
-        <v>57281</v>
+        <v>57351</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1747,25 +1745,21 @@
       <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Intagan, öster om, Vg</t>
+          <t>Risveden/Sopekärr, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>338000</v>
+        <v>338364</v>
       </c>
       <c r="R11" t="n">
-        <v>6433828</v>
+        <v>6433774</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1789,17 +1783,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Fann spillkråkehack efter födosök vid basen av ett medelgrovt torrträd. Stod ca 10 m söder om småvattnet i skogen.</t>
+          <t>Spår av födosökande spillkråka</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1814,126 +1808,15 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>120338516</v>
-      </c>
-      <c r="B12" t="n">
-        <v>57351</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Risveden/Sopekärr, Vg</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>338364</v>
-      </c>
-      <c r="R12" t="n">
-        <v>6433774</v>
-      </c>
-      <c r="S12" t="n">
-        <v>10</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Ale</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Västergötland</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Skepplanda</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Spår av födosökande spillkråka</t>
-        </is>
-      </c>
-      <c r="AD12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>Linus Lundin</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>Linus Lundin</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 7903-2024 artfynd.xlsx
+++ b/artfynd/A 7903-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1818,6 +1818,127 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128507246</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57682</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Mickelsdamm Skår, Mickelsdamm Skår, Vg</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>338136</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6433793</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>18:48</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>18:48</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 7903-2024 artfynd.xlsx
+++ b/artfynd/A 7903-2024 artfynd.xlsx
@@ -1823,7 +1823,7 @@
         <v>128507246</v>
       </c>
       <c r="B12" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 7903-2024 artfynd.xlsx
+++ b/artfynd/A 7903-2024 artfynd.xlsx
@@ -1823,7 +1823,7 @@
         <v>128507246</v>
       </c>
       <c r="B12" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 7903-2024 artfynd.xlsx
+++ b/artfynd/A 7903-2024 artfynd.xlsx
@@ -1823,7 +1823,7 @@
         <v>128507246</v>
       </c>
       <c r="B12" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 7903-2024 artfynd.xlsx
+++ b/artfynd/A 7903-2024 artfynd.xlsx
@@ -1823,7 +1823,7 @@
         <v>128507246</v>
       </c>
       <c r="B12" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 7903-2024 artfynd.xlsx
+++ b/artfynd/A 7903-2024 artfynd.xlsx
@@ -1349,7 +1349,7 @@
         <v>0</v>
       </c>
       <c r="AE7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG7" t="b">
         <v>0</v>

--- a/artfynd/A 7903-2024 artfynd.xlsx
+++ b/artfynd/A 7903-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,58 +675,57 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114953610</v>
+        <v>120403713</v>
       </c>
       <c r="B2" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>2667</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Spillkråka, Risveden, Vg</t>
+          <t>Mickelsdamm, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>338162</v>
+        <v>338122</v>
       </c>
       <c r="R2" t="n">
-        <v>6433815</v>
+        <v>6433725</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,17 +752,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2024-10-13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2024-10-13</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Spår av födosök på liten tall</t>
+          <t>på aspstammar och på sten i branten</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,77 +771,68 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Hällmarksbarrskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Anna Pielach</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Anna Pielach</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114953681</v>
+        <v>120403721</v>
       </c>
       <c r="B3" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96231</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>2779</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Spillkråka, Vg</t>
+          <t>Mickelsdamm, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>338021</v>
+        <v>338122</v>
       </c>
       <c r="R3" t="n">
-        <v>6433811</v>
+        <v>6433725</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,17 +859,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2024-10-13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Spår av födosök</t>
+          <t>2024-10-13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,18 +873,19 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Anna Pielach</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Anna Pielach</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -909,16 +895,11 @@
         <v>114953514</v>
       </c>
       <c r="B4" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1021,15 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>115074021</v>
+        <v>114953610</v>
       </c>
       <c r="B5" t="n">
-        <v>57624</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1037,16 +1013,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1054,28 +1030,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sopekärr/Intakan, Hålanda, Vg</t>
+          <t>Spillkråka, Risveden, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>338271</v>
+        <v>338162</v>
       </c>
       <c r="R5" t="n">
-        <v>6433813</v>
+        <v>6433815</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1099,12 +1075,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Spår av födosök på liten tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,6 +1096,11 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Hällmarksbarrskog</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1131,32 +1117,27 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>115073977</v>
+        <v>114953681</v>
       </c>
       <c r="B6" t="n">
-        <v>57412</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103020</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1164,32 +1145,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sopekärr/Intakan, Hålanda, Vg</t>
+          <t>Spillkråka, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>338266</v>
+        <v>338021</v>
       </c>
       <c r="R6" t="n">
-        <v>6433790</v>
+        <v>6433811</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1213,17 +1186,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Födosökande i tät gran/björk/tall skog.</t>
+          <t>Spår av födosök</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,49 +1223,40 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>116186066</v>
+        <v>116183973</v>
       </c>
       <c r="B7" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1302,13 +1266,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>338186</v>
+        <v>338203</v>
       </c>
       <c r="R7" t="n">
-        <v>6433810</v>
+        <v>6433836</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1332,24 +1296,24 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Hörde den väldigt kort sjunga, och såg den inte. Med tanke på den korta observationen ser jag den som något osäker. Vid nytt besök den 21 april såg eller hörde jag den inte i området.</t>
+          <t>Fann spillkråkehack efter födosök vid basen av ett klent talltorrträd.</t>
         </is>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="b">
         <v>0</v>
@@ -1369,15 +1333,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>116184951</v>
+        <v>116184071</v>
       </c>
       <c r="B8" t="n">
-        <v>57624</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,16 +1344,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1407,7 +1366,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1417,13 +1376,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>338325</v>
+        <v>338000</v>
       </c>
       <c r="R8" t="n">
-        <v>6433786</v>
+        <v>6433828</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1447,12 +1406,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-04-21</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Fann spillkråkehack efter födosök vid basen av ett medelgrovt torrträd. Stod ca 10 m söder om småvattnet i skogen.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1479,19 +1443,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>116183973</v>
+        <v>120338516</v>
       </c>
       <c r="B9" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1515,25 +1474,21 @@
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Intagan, öster om, Vg</t>
+          <t>Risveden/Sopekärr, Vg</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>338203</v>
+        <v>338364</v>
       </c>
       <c r="R9" t="n">
-        <v>6433836</v>
+        <v>6433774</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1557,17 +1512,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Fann spillkråkehack efter födosök vid basen av ett klent talltorrträd.</t>
+          <t>Spår av födosökande spillkråka</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1582,31 +1537,26 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>116184071</v>
+        <v>120338571</v>
       </c>
       <c r="B10" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1630,25 +1580,21 @@
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Intagan, öster om, Vg</t>
+          <t>Risveden/Sopekärr, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>338000</v>
+        <v>338470</v>
       </c>
       <c r="R10" t="n">
-        <v>6433828</v>
+        <v>6433759</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1672,17 +1618,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Fann spillkråkehack efter födosök vid basen av ett medelgrovt torrträd. Stod ca 10 m söder om småvattnet i skogen.</t>
+          <t>Spår av födosökand spillkråka vid basen på död gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1697,31 +1643,26 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Thomas Grönlund</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120338516</v>
+        <v>120755880</v>
       </c>
       <c r="B11" t="n">
-        <v>57351</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1742,21 +1683,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Risveden/Sopekärr, Vg</t>
+          <t>Mickelsdamm Skår, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>338364</v>
+        <v>338130</v>
       </c>
       <c r="R11" t="n">
-        <v>6433774</v>
+        <v>6433733</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1783,17 +1732,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Spår av födosökande spillkråka</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1804,16 +1748,21 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Grimhild Angertuva</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1823,11 +1772,11 @@
         <v>128507246</v>
       </c>
       <c r="B12" t="n">
-        <v>57720</v>
+        <v>57950</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1938,6 +1887,1001 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>120259571</v>
+      </c>
+      <c r="B13" t="n">
+        <v>56895</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100088</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vanlig snok</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Natrix natrix</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Intakan. öster om, Vg</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>338098</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6433731</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Låg stilla på ett stenblock invid en lodyta. Liten blockmiljö. Rörde sig men låg kvar på blocket när jag försiktigt petade på den. Snoken syns även i nedre kanten på miljöbilden.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>115074021</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Sopekärr/Intakan, Hålanda, Vg</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>338271</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6433813</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>116184951</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Intagan, öster om, Vg</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>338325</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6433786</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-03-17</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-03-17</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>120259576</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Intakan, öster om, Vg</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>338216</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6433731</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ingick i ett litet meståg.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>120329674</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Risveden/Sopekärr, Vg</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>338302</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6433745</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-10-01</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>120755916</v>
+      </c>
+      <c r="B18" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Mickelsdamm Skår, Vg</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>338413</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6433754</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-05-13</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-05-13</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>115073977</v>
+      </c>
+      <c r="B19" t="n">
+        <v>58112</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Sopekärr/Intakan, Hålanda, Vg</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>338266</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6433790</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Födosökande i tät gran/björk/tall skog.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>116186066</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Intagan, öster om, Vg</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>338186</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6433810</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-03-17</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-03-17</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Hörde den väldigt kort sjunga, och såg den inte. Med tanke på den korta observationen ser jag den som något osäker. Vid nytt besök den 21 april såg eller hörde jag den inte i området.</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Thomas Grönlund</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>125474021</v>
+      </c>
+      <c r="B21" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Mickelsdamm  Sopekärr , Vg</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>338185</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6433735</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Gångar på liggande björklåga vid Sopekärr</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Grimhild Angertuva</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 7903-2024 artfynd.xlsx
+++ b/artfynd/A 7903-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120403713</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -889,6 +899,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120403721</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -999,6 +1014,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114953514</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1114,6 +1134,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114953610</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1220,6 +1245,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114953681</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1330,6 +1360,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116183973</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1440,6 +1475,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116184071</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1546,6 +1586,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120338516</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1652,6 +1697,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120338571</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1766,6 +1816,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120755880</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1887,6 +1942,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128507246</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2011,6 +2071,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120259571</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2116,6 +2181,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115074021</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2221,6 +2291,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116184951</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2327,6 +2402,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120259576</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2428,6 +2508,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120329674</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2542,6 +2627,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120755916</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2656,6 +2746,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115073977</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2770,6 +2865,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116186066</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2882,8 +2982,35 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125474021</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>